--- a/ThesisStudy2Exp1_Stim.xlsx
+++ b/ThesisStudy2Exp1_Stim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicktarantino/Desktop/ThesisProject_Study2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3EFEAF-FB48-F748-BC17-B8ABE411364C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63298C39-46DF-3648-BB38-5B73FC04BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
   </bookViews>

--- a/ThesisStudy2Exp1_Stim.xlsx
+++ b/ThesisStudy2Exp1_Stim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicktarantino/Desktop/ThesisProject_Study2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63298C39-46DF-3648-BB38-5B73FC04BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786E0F80-2454-C147-9905-F3B6E48A1F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
   </bookViews>

--- a/ThesisStudy2Exp1_Stim.xlsx
+++ b/ThesisStudy2Exp1_Stim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicktarantino/Desktop/ThesisProject_Study2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786E0F80-2454-C147-9905-F3B6E48A1F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDF258E-90A8-F24D-86E8-BA4DCA4CBB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
   </bookViews>
@@ -440,19 +440,19 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="C9">
-        <f>B9+5</f>
-        <v>7.5</v>
+        <f>B9+(2.85*2)</f>
+        <v>8.5500000000000007</v>
       </c>
       <c r="D9">
-        <f>C9+5</f>
-        <v>12.5</v>
+        <f>C9+(2.85*2)</f>
+        <v>14.25</v>
       </c>
       <c r="E9">
-        <f>D9+5</f>
-        <v>17.5</v>
+        <f>D9+(2.85*2)</f>
+        <v>19.95</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -461,19 +461,19 @@
       </c>
       <c r="B10">
         <f>B9-1</f>
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="C10">
         <f>C9-1</f>
-        <v>6.5</v>
+        <v>7.5500000000000007</v>
       </c>
       <c r="D10">
         <f>D9-1</f>
-        <v>11.5</v>
+        <v>13.25</v>
       </c>
       <c r="E10">
         <f>E9-1</f>
-        <v>16.5</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -482,19 +482,19 @@
       </c>
       <c r="B11">
         <f>B9+1</f>
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="C11">
         <f>C9+1</f>
-        <v>8.5</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="D11">
         <f>D9+1</f>
-        <v>13.5</v>
+        <v>15.25</v>
       </c>
       <c r="E11">
         <f>E9+1</f>
-        <v>18.5</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -503,19 +503,19 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" ref="B13:E15" si="0">TAN(RADIANS(B9))</f>
-        <v>4.3660942908512058E-2</v>
+        <v>4.9782949026111224E-2</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
-        <v>0.13165249758739583</v>
+        <v>0.15034327406196593</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>0.22169466264293991</v>
+        <v>0.25396764647494369</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>0.31529878887898349</v>
+        <v>0.3629822775252422</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -524,19 +524,19 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>2.6185921569186928E-2</v>
+        <v>3.2299816700350079E-2</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
-        <v>0.11393560830164549</v>
+        <v>0.13254038980238333</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>0.20345229942369938</v>
+        <v>0.23546874348332675</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>0.29621349496208027</v>
+        <v>0.34335177720598992</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -545,19 +545,19 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>6.1162620150484313E-2</v>
+        <v>6.7296492224285243E-2</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
-        <v>0.14945100134912781</v>
+        <v>0.16823984266821759</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>0.24007875908011603</v>
+        <v>0.27263129185209495</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>0.33459531950207316</v>
+        <v>0.38286311692082686</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -566,19 +566,19 @@
       </c>
       <c r="B16" s="2">
         <f>B15-B14</f>
-        <v>3.4976698581297386E-2</v>
+        <v>3.4996675523935164E-2</v>
       </c>
       <c r="C16" s="2">
         <f>C15-C14</f>
-        <v>3.5515393047482316E-2</v>
+        <v>3.5699452865834258E-2</v>
       </c>
       <c r="D16" s="2">
         <f>D15-D14</f>
-        <v>3.6626459656416643E-2</v>
+        <v>3.71625483687682E-2</v>
       </c>
       <c r="E16" s="2">
         <f>E15-E14</f>
-        <v>3.8381824539992893E-2</v>
+        <v>3.9511339714836946E-2</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">

--- a/ThesisStudy2Exp1_Stim.xlsx
+++ b/ThesisStudy2Exp1_Stim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicktarantino/Desktop/ThesisProject_Study2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDF258E-90A8-F24D-86E8-BA4DCA4CBB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94DE6EA-AEEA-EE48-8D08-C87C9978B473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
   </bookViews>
@@ -440,19 +440,19 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="C9">
-        <f>B9+(2.85*2)</f>
-        <v>8.5500000000000007</v>
+        <f>B9+(2.5*2)</f>
+        <v>7.5</v>
       </c>
       <c r="D9">
-        <f>C9+(2.85*2)</f>
-        <v>14.25</v>
+        <f>C9+(2.5*2)</f>
+        <v>12.5</v>
       </c>
       <c r="E9">
-        <f>D9+(2.85*2)</f>
-        <v>19.95</v>
+        <f>D9+(2.5*2)</f>
+        <v>17.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -461,19 +461,19 @@
       </c>
       <c r="B10">
         <f>B9-1</f>
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="C10">
         <f>C9-1</f>
-        <v>7.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="D10">
         <f>D9-1</f>
-        <v>13.25</v>
+        <v>11.5</v>
       </c>
       <c r="E10">
         <f>E9-1</f>
-        <v>18.95</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -482,19 +482,19 @@
       </c>
       <c r="B11">
         <f>B9+1</f>
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="C11">
         <f>C9+1</f>
-        <v>9.5500000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="D11">
         <f>D9+1</f>
-        <v>15.25</v>
+        <v>13.5</v>
       </c>
       <c r="E11">
         <f>E9+1</f>
-        <v>20.95</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -503,19 +503,19 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" ref="B13:E15" si="0">TAN(RADIANS(B9))</f>
-        <v>4.9782949026111224E-2</v>
+        <v>4.3660942908512058E-2</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
-        <v>0.15034327406196593</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>0.25396764647494369</v>
+        <v>0.22169466264293991</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>0.3629822775252422</v>
+        <v>0.31529878887898349</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -524,19 +524,19 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>3.2299816700350079E-2</v>
+        <v>2.6185921569186928E-2</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
-        <v>0.13254038980238333</v>
+        <v>0.11393560830164549</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>0.23546874348332675</v>
+        <v>0.20345229942369938</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>0.34335177720598992</v>
+        <v>0.29621349496208027</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -545,19 +545,19 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>6.7296492224285243E-2</v>
+        <v>6.1162620150484313E-2</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
-        <v>0.16823984266821759</v>
+        <v>0.14945100134912781</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>0.27263129185209495</v>
+        <v>0.24007875908011603</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>0.38286311692082686</v>
+        <v>0.33459531950207316</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -566,19 +566,19 @@
       </c>
       <c r="B16" s="2">
         <f>B15-B14</f>
-        <v>3.4996675523935164E-2</v>
+        <v>3.4976698581297386E-2</v>
       </c>
       <c r="C16" s="2">
         <f>C15-C14</f>
-        <v>3.5699452865834258E-2</v>
+        <v>3.5515393047482316E-2</v>
       </c>
       <c r="D16" s="2">
         <f>D15-D14</f>
-        <v>3.71625483687682E-2</v>
+        <v>3.6626459656416643E-2</v>
       </c>
       <c r="E16" s="2">
         <f>E15-E14</f>
-        <v>3.9511339714836946E-2</v>
+        <v>3.8381824539992893E-2</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
